--- a/tmp_data/全市学区招生服务范围描述.xlsx
+++ b/tmp_data/全市学区招生服务范围描述.xlsx
@@ -11,7 +11,7 @@
     <sheet name="WpsReserved_CellImgList" sheetId="4" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">全市!$A$1:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">全市!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="404">
   <si>
     <t>序号</t>
   </si>
@@ -659,46 +659,7 @@
     <t>先锋街道中心村、建新村和金塘村（建设北路延长线左边部分）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>风车坪东校区</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="汉仪书宋二KW"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中学部</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="汉仪书宋二KW"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
+    <t>风车坪万楼学校（中学部）</t>
   </si>
   <si>
     <t>3143019755_middle</t>
@@ -1656,15 +1617,12 @@
     <t>桐梓村、高岭社区、先锋乡农场、狮山村、湘大社区、红旗村、卫星村、响水村、湘大教职工子弟</t>
   </si>
   <si>
-    <t>长沙市一中九华中学</t>
+    <t>湘潭市九华中学</t>
   </si>
   <si>
     <t>3143001022_middle</t>
   </si>
   <si>
-    <t>湘潭市九华中学</t>
-  </si>
-  <si>
     <t>将军渡社区、桃李社区、杉山社区、郑家村、红星村、民乐社区、星沙村、塘高村、映山村、响水村</t>
   </si>
   <si>
@@ -1675,6 +1633,24 @@
   </si>
   <si>
     <t>雨湖路社区、车站路社区、关圣殿社区</t>
+  </si>
+  <si>
+    <t>保利学校</t>
+  </si>
+  <si>
+    <t>10000000_middle</t>
+  </si>
+  <si>
+    <t>1.船形山社区（原雅礼中学范围）；2.杉山社区（杉山社区是九华一中范围，该范围内愿意就读保利时代学校的可以报九华保利学校）。</t>
+  </si>
+  <si>
+    <t>湘江中学</t>
+  </si>
+  <si>
+    <t>10000001_middle</t>
+  </si>
+  <si>
+    <t>湘潭市北边界—伏林大道—白云路—沪昆高铁—长潭西高速—九昭路—沿江北路围成的区域，涉及的乡镇街道为鹤岭镇、响水乡、九华街道、和平街道部分区域。</t>
   </si>
 </sst>
 </file>
@@ -1900,6 +1876,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
@@ -1917,13 +1900,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="汉仪书宋二KW"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2127,7 +2103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2160,6 +2136,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2287,7 +2278,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
@@ -2299,34 +2290,34 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="8">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
@@ -2411,7 +2402,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2481,6 +2472,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2793,7 +2793,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="32.1416666666667" customWidth="1"/>
@@ -5054,10 +5054,10 @@
         <v>393</v>
       </c>
       <c r="E98" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>394</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>152</v>
@@ -5068,21 +5068,67 @@
         <v>99</v>
       </c>
       <c r="B99" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C99" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="10" t="s">
+      <c r="E99" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="F99" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="E99" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="F99" s="11" t="s">
+      <c r="G99" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="100" ht="27" spans="1:7">
+      <c r="A100" s="7">
+        <v>100</v>
+      </c>
+      <c r="B100" s="23" t="s">
         <v>398</v>
       </c>
-      <c r="G99" s="15" t="s">
+      <c r="C100" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="E100" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="F100" s="24" t="s">
+        <v>400</v>
+      </c>
+      <c r="G100" s="24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" ht="27" spans="1:7">
+      <c r="A101" s="7">
+        <v>101</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="E101" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="F101" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="G101" s="24" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5091,7 +5137,7 @@
   <protectedRanges>
     <protectedRange sqref="A1:G35 A100:G1048574" name="Range1"/>
   </protectedRanges>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G99" etc:filterBottomFollowUsedRange="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G101" etc:filterBottomFollowUsedRange="1">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tmp_data/全市学区招生服务范围描述.xlsx
+++ b/tmp_data/全市学区招生服务范围描述.xlsx
@@ -1638,7 +1638,7 @@
     <t>保利学校</t>
   </si>
   <si>
-    <t>10000000_middle</t>
+    <t>10000000_union</t>
   </si>
   <si>
     <t>1.船形山社区（原雅礼中学范围）；2.杉山社区（杉山社区是九华一中范围，该范围内愿意就读保利时代学校的可以报九华保利学校）。</t>
@@ -1876,13 +1876,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
@@ -2402,7 +2402,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2472,9 +2472,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5090,22 +5087,22 @@
       <c r="A100" s="7">
         <v>100</v>
       </c>
-      <c r="B100" s="23" t="s">
+      <c r="B100" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="C100" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D100" s="23" t="s">
+      <c r="C100" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D100" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="E100" s="23" t="s">
+      <c r="E100" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="F100" s="24" t="s">
+      <c r="F100" s="23" t="s">
         <v>400</v>
       </c>
-      <c r="G100" s="24" t="s">
+      <c r="G100" s="23" t="s">
         <v>152</v>
       </c>
     </row>
@@ -5113,29 +5110,29 @@
       <c r="A101" s="7">
         <v>101</v>
       </c>
-      <c r="B101" s="23" t="s">
+      <c r="B101" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D101" s="23" t="s">
+      <c r="D101" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="E101" s="23" t="s">
+      <c r="E101" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="F101" s="25" t="s">
+      <c r="F101" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="G101" s="24" t="s">
+      <c r="G101" s="23" t="s">
         <v>152</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
-    <protectedRange sqref="A1:G35 A100:G1048574" name="Range1"/>
+    <protectedRange sqref="A1:G35 A100:G100 A101:G1048574" name="Range1"/>
   </protectedRanges>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G101" etc:filterBottomFollowUsedRange="1">
     <extLst/>

--- a/tmp_data/全市学区招生服务范围描述.xlsx
+++ b/tmp_data/全市学区招生服务范围描述.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="30720" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="全市" sheetId="1" r:id="rId1"/>
     <sheet name="WpsReserved_CellImgList" sheetId="4" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">全市!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">全市!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="410">
   <si>
     <t>序号</t>
   </si>
@@ -1605,18 +1605,27 @@
     <t>杉树巷社区、和平社区、建设社区、南盘岭社区、韶山路社区、公园社区、中心社区、福利社区、烟竹社区、科大社区</t>
   </si>
   <si>
+    <t>湘潭大学附属实验学校（小学）</t>
+  </si>
+  <si>
+    <t>十二年一贯制学校</t>
+  </si>
+  <si>
+    <t>3443000270_union</t>
+  </si>
+  <si>
     <t>湘潭大学附属实验学校</t>
   </si>
   <si>
-    <t>十二年一贯制学校</t>
-  </si>
-  <si>
-    <t>3443000270_union</t>
-  </si>
-  <si>
     <t>桐梓村、高岭社区、先锋乡农场、狮山村、湘大社区、红旗村、卫星村、响水村、湘大教职工子弟</t>
   </si>
   <si>
+    <t>湘潭大学附属实验学校（中学）</t>
+  </si>
+  <si>
+    <t>3443000270_middle</t>
+  </si>
+  <si>
     <t>湘潭市九华中学</t>
   </si>
   <si>
@@ -1635,13 +1644,22 @@
     <t>雨湖路社区、车站路社区、关圣殿社区</t>
   </si>
   <si>
+    <t>保利学校（小学）</t>
+  </si>
+  <si>
+    <t>10000000_union</t>
+  </si>
+  <si>
     <t>保利学校</t>
   </si>
   <si>
-    <t>10000000_union</t>
-  </si>
-  <si>
     <t>1.船形山社区（原雅礼中学范围）；2.杉山社区（杉山社区是九华一中范围，该范围内愿意就读保利时代学校的可以报九华保利学校）。</t>
+  </si>
+  <si>
+    <t>保利学校（中学）</t>
+  </si>
+  <si>
+    <t>10000000_middle</t>
   </si>
   <si>
     <t>湘江中学</t>
@@ -1876,6 +1894,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="汉仪书宋二KW"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
@@ -1886,13 +1911,6 @@
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="汉仪书宋二KW"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2790,15 +2808,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H101"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H103"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="32.1416666666667" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="32.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="16.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="5" width="32.75" style="3" customWidth="1"/>
     <col min="6" max="6" width="73.75" style="4" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
+    <col min="7" max="7" width="16.6296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="29" customHeight="1" spans="1:8">
@@ -4875,7 +4893,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="91" ht="54" spans="1:8">
+    <row r="91" ht="72" spans="1:8">
       <c r="A91" s="7">
         <v>91</v>
       </c>
@@ -5028,10 +5046,10 @@
         <v>390</v>
       </c>
       <c r="E97" s="19" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G97" s="15" t="s">
         <v>152</v>
@@ -5039,22 +5057,22 @@
     </row>
     <row r="98" s="1" customFormat="1" ht="71.25" customHeight="1" spans="1:7">
       <c r="A98" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="F98" s="11" t="s">
         <v>392</v>
-      </c>
-      <c r="C98" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="E98" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="F98" s="11" t="s">
-        <v>394</v>
       </c>
       <c r="G98" s="15" t="s">
         <v>152</v>
@@ -5062,13 +5080,13 @@
     </row>
     <row r="99" s="1" customFormat="1" ht="71.25" customHeight="1" spans="1:7">
       <c r="A99" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>395</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>396</v>
@@ -5083,58 +5101,104 @@
         <v>152</v>
       </c>
     </row>
-    <row r="100" ht="27" spans="1:7">
+    <row r="100" s="1" customFormat="1" ht="71.25" customHeight="1" spans="1:7">
       <c r="A100" s="7">
-        <v>100</v>
-      </c>
-      <c r="B100" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>75</v>
+      <c r="C100" s="19" t="s">
+        <v>9</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="F100" s="23" t="s">
+      <c r="F100" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="G100" s="23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="101" ht="27" spans="1:7">
+      <c r="G100" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" ht="28.8" spans="1:7">
       <c r="A101" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>401</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>402</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F101" s="24" t="s">
         <v>403</v>
       </c>
+      <c r="F101" s="23" t="s">
+        <v>404</v>
+      </c>
       <c r="G101" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="102" ht="28.8" spans="1:7">
+      <c r="A102" s="7">
+        <v>100</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F102" s="23" t="s">
+        <v>404</v>
+      </c>
+      <c r="G102" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" ht="28.8" spans="1:7">
+      <c r="A103" s="7">
+        <v>101</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F103" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="G103" s="23" t="s">
         <v>152</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
-    <protectedRange sqref="A1:G35 A100:G100 A101:G1048574" name="Range1"/>
+    <protectedRange sqref="A1:G35 A101:G101 A103:G1048576" name="Range1"/>
   </protectedRanges>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G101" etc:filterBottomFollowUsedRange="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G103" etc:filterBottomFollowUsedRange="1">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5147,7 +5211,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
